--- a/data/trans_orig/IMC_Medido-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Clase-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores medido</t>
+          <t>Índice de masa corporal (IMC) medio de los menores medido (tasa de respuesta: 78,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,04; 21,17</t>
+          <t>19,07; 20,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,73; 18,95</t>
+          <t>17,71; 18,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,67; 19,38</t>
+          <t>17,63; 19,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,52; 20,5</t>
+          <t>18,51; 20,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,56; 18,78</t>
+          <t>17,54; 18,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,07; 20,43</t>
+          <t>18,1; 20,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,98; 20,43</t>
+          <t>19,04; 20,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,79; 18,64</t>
+          <t>17,77; 18,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,13; 19,6</t>
+          <t>18,15; 19,6</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,06; 20,86</t>
+          <t>18,06; 20,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,48; 18,67</t>
+          <t>17,41; 18,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,48; 19,07</t>
+          <t>17,45; 18,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,85; 20,37</t>
+          <t>18,77; 20,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,36; 18,55</t>
+          <t>17,41; 18,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,65; 19,3</t>
+          <t>17,67; 19,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,71; 20,27</t>
+          <t>18,67; 20,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,58; 18,41</t>
+          <t>17,55; 18,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,76; 18,88</t>
+          <t>17,78; 18,9</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,29; 20,1</t>
+          <t>18,24; 20,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,26; 19,17</t>
+          <t>17,26; 19,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,43; 22,04</t>
+          <t>17,43; 21,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,55; 21,98</t>
+          <t>19,57; 21,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,13; 21,38</t>
+          <t>18,99; 21,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,98; 20,92</t>
+          <t>17,94; 20,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,19; 20,63</t>
+          <t>19,13; 20,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,48; 20,06</t>
+          <t>18,5; 19,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,1; 20,51</t>
+          <t>18,02; 20,42</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,86; 19,91</t>
+          <t>18,88; 19,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,58; 19,8</t>
+          <t>18,59; 19,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,07; 22,27</t>
+          <t>18,95; 22,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,33; 20,36</t>
+          <t>19,29; 20,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,48; 19,63</t>
+          <t>18,56; 19,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,68; 20,44</t>
+          <t>18,84; 20,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,23; 20,04</t>
+          <t>19,2; 19,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,67; 19,5</t>
+          <t>18,66; 19,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,25; 21,48</t>
+          <t>19,18; 21,34</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,15; 20,6</t>
+          <t>19,12; 20,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,25; 19,32</t>
+          <t>18,3; 19,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,83; 20,69</t>
+          <t>18,82; 20,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,05; 20,46</t>
+          <t>19,07; 20,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,41; 19,62</t>
+          <t>18,37; 19,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,4; 21,27</t>
+          <t>19,37; 21,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,33; 20,25</t>
+          <t>19,3; 20,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,49; 19,3</t>
+          <t>18,49; 19,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,41; 20,85</t>
+          <t>19,4; 20,84</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,76; 22,12</t>
+          <t>19,88; 22,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,03; 20,81</t>
+          <t>18,99; 20,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,74; 21,62</t>
+          <t>17,67; 21,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,16; 20,71</t>
+          <t>19,27; 20,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,08; 21,52</t>
+          <t>19,12; 21,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,73; 21,77</t>
+          <t>18,67; 21,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,74; 21,05</t>
+          <t>19,7; 20,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,22; 20,81</t>
+          <t>19,3; 20,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,59; 21,02</t>
+          <t>18,54; 20,97</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,28; 19,97</t>
+          <t>19,24; 19,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,47; 19,03</t>
+          <t>18,49; 19,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,8; 20,58</t>
+          <t>18,79; 20,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,51; 20,11</t>
+          <t>19,49; 20,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,62; 19,22</t>
+          <t>18,63; 19,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,02; 19,88</t>
+          <t>19,02; 19,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,47; 19,94</t>
+          <t>19,49; 19,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,63; 19,04</t>
+          <t>18,62; 19,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,1; 20,13</t>
+          <t>19,04; 20,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_Medido-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Clase-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores medido (tasa de respuesta: 78,69%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 78,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,07; 20,98</t>
+          <t>18,95; 21,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,71; 18,98</t>
+          <t>17,72; 18,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,63; 19,37</t>
+          <t>17,69; 19,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,51; 20,46</t>
+          <t>18,56; 20,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,54; 18,73</t>
+          <t>17,58; 18,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,1; 20,39</t>
+          <t>18,05; 20,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,04; 20,55</t>
+          <t>19,01; 20,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,77; 18,68</t>
+          <t>17,75; 18,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,15; 19,6</t>
+          <t>18,16; 19,64</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,06; 20,81</t>
+          <t>18,06; 21,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,41; 18,63</t>
+          <t>17,43; 18,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,45; 18,99</t>
+          <t>17,49; 19,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,77; 20,35</t>
+          <t>18,87; 20,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,41; 18,52</t>
+          <t>17,38; 18,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,67; 19,24</t>
+          <t>17,69; 19,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,67; 20,31</t>
+          <t>18,66; 20,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,55; 18,39</t>
+          <t>17,56; 18,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,78; 18,9</t>
+          <t>17,77; 18,89</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,24; 20,15</t>
+          <t>18,34; 20,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,26; 19,2</t>
+          <t>17,24; 19,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,43; 21,88</t>
+          <t>17,5; 21,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,57; 21,78</t>
+          <t>19,6; 22,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,99; 21,4</t>
+          <t>19,01; 21,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,94; 20,65</t>
+          <t>17,84; 20,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,13; 20,66</t>
+          <t>19,08; 20,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,97</t>
+          <t>18,5; 20,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,02; 20,42</t>
+          <t>18,14; 20,41</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,88; 19,9</t>
+          <t>18,85; 19,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,59; 19,84</t>
+          <t>18,55; 19,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,95; 22,28</t>
+          <t>18,93; 22,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,29; 20,4</t>
+          <t>19,25; 20,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,56; 19,7</t>
+          <t>18,51; 19,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,84; 20,52</t>
+          <t>18,75; 20,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,2; 19,97</t>
+          <t>19,21; 20,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,66; 19,53</t>
+          <t>18,68; 19,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,18; 21,34</t>
+          <t>19,2; 21,53</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,12; 20,57</t>
+          <t>19,14; 20,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,3; 19,37</t>
+          <t>18,29; 19,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,82; 20,78</t>
+          <t>18,84; 20,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,07; 20,46</t>
+          <t>19,08; 20,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,37; 19,63</t>
+          <t>18,41; 19,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,37; 21,29</t>
+          <t>19,33; 21,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,3; 20,28</t>
+          <t>19,29; 20,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,49; 19,32</t>
+          <t>18,49; 19,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,4; 20,84</t>
+          <t>19,37; 20,71</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,88; 22,15</t>
+          <t>19,74; 22,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,99; 20,75</t>
+          <t>18,93; 20,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,67; 21,58</t>
+          <t>17,76; 21,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,27; 20,67</t>
+          <t>19,18; 20,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,12; 21,5</t>
+          <t>19,11; 21,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,67; 21,87</t>
+          <t>18,67; 21,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,7; 20,96</t>
+          <t>19,68; 21,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,3; 20,8</t>
+          <t>19,24; 20,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,54; 20,97</t>
+          <t>18,59; 21,02</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,24; 19,95</t>
+          <t>19,23; 19,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,49; 19,04</t>
+          <t>18,48; 19,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,67</t>
+          <t>18,78; 20,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,49; 20,15</t>
+          <t>19,51; 20,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,63; 19,22</t>
+          <t>18,63; 19,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,02; 19,96</t>
+          <t>19,03; 19,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,49; 19,96</t>
+          <t>19,46; 19,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,62; 19,04</t>
+          <t>18,64; 19,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,04; 20,09</t>
+          <t>19,08; 20,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_Medido-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Clase-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19,34</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18,14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18,99</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>19,9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>18,3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18,48</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19,34</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,14</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,92</t>
+          <t>18,54</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18,74</t>
+          <t>18,8</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,95; 21,11</t>
+          <t>18,52; 20,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,72; 18,96</t>
+          <t>17,56; 18,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,69; 19,48</t>
+          <t>18,13; 20,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,56; 20,55</t>
+          <t>19,04; 21,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,58; 18,78</t>
+          <t>17,73; 18,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,05; 20,36</t>
+          <t>17,72; 19,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,01; 20,41</t>
+          <t>18,98; 20,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,75; 18,64</t>
+          <t>17,79; 18,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,16; 19,64</t>
+          <t>18,18; 19,66</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19,58</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17,94</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18,53</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>18,93</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>17,99</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>18,22</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,58</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17,94</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,4</t>
+          <t>18,29</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18,31</t>
+          <t>18,41</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,06; 21,11</t>
+          <t>18,85; 20,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,43; 18,68</t>
+          <t>17,36; 18,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,49; 19,07</t>
+          <t>17,75; 19,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,87; 20,5</t>
+          <t>18,06; 20,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,38; 18,53</t>
+          <t>17,48; 18,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,69; 19,33</t>
+          <t>17,55; 19,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,66; 20,27</t>
+          <t>18,71; 20,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,56; 18,39</t>
+          <t>17,58; 18,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,77; 18,89</t>
+          <t>17,85; 19,0</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,57</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19,98</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19,53</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>19,15</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>18,08</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19,06</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20,57</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,98</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>19,21</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19,15</t>
+          <t>19,41</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,34; 20,22</t>
+          <t>19,55; 21,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,24; 19,02</t>
+          <t>19,13; 21,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,5; 21,78</t>
+          <t>18,42; 21,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,6; 22,0</t>
+          <t>18,29; 20,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,01; 21,25</t>
+          <t>17,26; 19,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,84; 20,69</t>
+          <t>17,69; 21,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,08; 20,6</t>
+          <t>19,19; 20,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,5; 20,03</t>
+          <t>18,48; 20,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,14; 20,41</t>
+          <t>18,39; 20,69</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,79</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19,03</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19,54</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>19,35</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>19,1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20,52</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19,79</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,03</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,56</t>
+          <t>19,22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20,07</t>
+          <t>19,39</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,85; 19,94</t>
+          <t>19,33; 20,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,55; 19,86</t>
+          <t>18,48; 19,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,93; 22,4</t>
+          <t>18,66; 20,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,25; 20,36</t>
+          <t>18,86; 19,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,51; 19,59</t>
+          <t>18,58; 19,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,75; 20,48</t>
+          <t>18,31; 20,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,21; 20,0</t>
+          <t>19,23; 20,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,53</t>
+          <t>18,67; 19,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,2; 21,53</t>
+          <t>18,73; 20,13</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19,74</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18,97</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20,34</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>19,81</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>18,81</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19,71</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19,74</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,97</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,23</t>
+          <t>19,95</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20,02</t>
+          <t>20,18</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,14; 20,46</t>
+          <t>19,05; 20,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,29; 19,4</t>
+          <t>18,41; 19,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,84; 20,91</t>
+          <t>19,46; 21,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,08; 20,5</t>
+          <t>19,15; 20,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,41; 19,62</t>
+          <t>18,25; 19,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,33; 21,2</t>
+          <t>19,0; 20,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,29; 20,29</t>
+          <t>19,33; 20,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,49; 19,28</t>
+          <t>18,49; 19,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,37; 20,71</t>
+          <t>19,52; 20,98</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19,96</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19,98</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20,41</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>20,88</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>19,78</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18,91</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19,96</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19,98</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,03</t>
+          <t>19,03</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19,56</t>
+          <t>19,8</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,74; 22,03</t>
+          <t>19,16; 20,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,93; 20,76</t>
+          <t>19,08; 21,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,76; 21,52</t>
+          <t>19,13; 22,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,18; 20,64</t>
+          <t>19,76; 22,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,11; 21,69</t>
+          <t>19,03; 20,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,67; 21,83</t>
+          <t>17,87; 21,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,68; 21,01</t>
+          <t>19,74; 21,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,24; 20,84</t>
+          <t>19,22; 20,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,59; 21,02</t>
+          <t>18,83; 21,22</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>19,8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18,92</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19,55</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>19,57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>18,74</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>19,49</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>19,8</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>18,92</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,43</t>
+          <t>19,04</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19,46</t>
+          <t>19,32</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,23; 19,96</t>
+          <t>19,51; 20,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,48; 19,05</t>
+          <t>18,62; 19,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,78; 20,63</t>
+          <t>19,13; 20,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,51; 20,13</t>
+          <t>19,28; 19,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,63; 19,23</t>
+          <t>18,47; 19,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,03; 19,89</t>
+          <t>18,61; 19,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,46; 19,93</t>
+          <t>19,47; 19,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,64; 19,05</t>
+          <t>18,63; 19,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,08; 20,03</t>
+          <t>19,02; 19,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_Medido-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Clase-trans_orig.xlsx
@@ -528,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 81,88%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 78,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
